--- a/artfynd/A 60293-2025 artfynd.xlsx
+++ b/artfynd/A 60293-2025 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>130333817</v>
       </c>
       <c r="B5" t="n">
-        <v>83141</v>
+        <v>83144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60293-2025 artfynd.xlsx
+++ b/artfynd/A 60293-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130333780</v>
       </c>
       <c r="B2" t="n">
-        <v>57983</v>
+        <v>58009</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>130333857</v>
       </c>
       <c r="B3" t="n">
-        <v>58258</v>
+        <v>58284</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>130333817</v>
       </c>
       <c r="B5" t="n">
-        <v>83144</v>
+        <v>83170</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60293-2025 artfynd.xlsx
+++ b/artfynd/A 60293-2025 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>130333817</v>
       </c>
       <c r="B5" t="n">
-        <v>83170</v>
+        <v>83171</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60293-2025 artfynd.xlsx
+++ b/artfynd/A 60293-2025 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>130333817</v>
       </c>
       <c r="B5" t="n">
-        <v>83171</v>
+        <v>83172</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60293-2025 artfynd.xlsx
+++ b/artfynd/A 60293-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130333780</v>
       </c>
       <c r="B2" t="n">
-        <v>58009</v>
+        <v>58011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>130333857</v>
       </c>
       <c r="B3" t="n">
-        <v>58284</v>
+        <v>58286</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>130333817</v>
       </c>
       <c r="B5" t="n">
-        <v>83172</v>
+        <v>83174</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60293-2025 artfynd.xlsx
+++ b/artfynd/A 60293-2025 artfynd.xlsx
@@ -784,46 +784,39 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130333857</v>
+        <v>130333842</v>
       </c>
       <c r="B3" t="n">
-        <v>58286</v>
+        <v>8440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103001</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -831,13 +824,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334513</v>
+        <v>334546</v>
       </c>
       <c r="R3" t="n">
-        <v>6432789</v>
+        <v>6432714</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,6 +868,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -893,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130333842</v>
+        <v>130333817</v>
       </c>
       <c r="B4" t="n">
-        <v>8440</v>
+        <v>83174</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,28 +898,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>6439</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -933,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>334546</v>
+        <v>334519</v>
       </c>
       <c r="R4" t="n">
-        <v>6432714</v>
+        <v>6432715</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,6 +972,21 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -996,37 +1003,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130333817</v>
+        <v>130333857</v>
       </c>
       <c r="B5" t="n">
-        <v>83174</v>
+        <v>58286</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6439</v>
+        <v>103001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1034,13 +1050,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>334519</v>
+        <v>334513</v>
       </c>
       <c r="R5" t="n">
-        <v>6432715</v>
+        <v>6432789</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,24 +1094,8 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">

--- a/artfynd/A 60293-2025 artfynd.xlsx
+++ b/artfynd/A 60293-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130333780</v>
       </c>
       <c r="B2" t="n">
-        <v>58011</v>
+        <v>58019</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>130333817</v>
       </c>
       <c r="B4" t="n">
-        <v>83174</v>
+        <v>83182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>130333857</v>
       </c>
       <c r="B5" t="n">
-        <v>58286</v>
+        <v>58294</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60293-2025 artfynd.xlsx
+++ b/artfynd/A 60293-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130333780</v>
       </c>
       <c r="B2" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>130333817</v>
       </c>
       <c r="B4" t="n">
-        <v>83182</v>
+        <v>83183</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>130333857</v>
       </c>
       <c r="B5" t="n">
-        <v>58294</v>
+        <v>58295</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60293-2025 artfynd.xlsx
+++ b/artfynd/A 60293-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130333780</v>
       </c>
       <c r="B2" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>130333817</v>
       </c>
       <c r="B4" t="n">
-        <v>83183</v>
+        <v>83184</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>130333857</v>
       </c>
       <c r="B5" t="n">
-        <v>58295</v>
+        <v>58296</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60293-2025 artfynd.xlsx
+++ b/artfynd/A 60293-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130333780</v>
+        <v>130333753</v>
       </c>
       <c r="B2" t="n">
-        <v>58021</v>
+        <v>85532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,35 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>1971</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Stor sotdyna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Camarops polysperma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Mont.) J.H.Mill.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>334597</v>
+        <v>334599</v>
       </c>
       <c r="R2" t="n">
-        <v>6432745</v>
+        <v>6432729</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,8 +757,24 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -784,39 +791,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130333842</v>
+        <v>130333762</v>
       </c>
       <c r="B3" t="n">
-        <v>8440</v>
+        <v>85532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>1971</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stor sotdyna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Camarops polysperma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Mont.) J.H.Mill.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334546</v>
+        <v>334617</v>
       </c>
       <c r="R3" t="n">
-        <v>6432714</v>
+        <v>6432745</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,6 +876,21 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -887,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130333817</v>
+        <v>130333833</v>
       </c>
       <c r="B4" t="n">
-        <v>83184</v>
+        <v>75300</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +918,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6439</v>
+        <v>6428</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>334519</v>
+        <v>334532</v>
       </c>
       <c r="R4" t="n">
-        <v>6432715</v>
+        <v>6432699</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,17 +995,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>klibbal</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1003,46 +1023,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130333857</v>
+        <v>130333817</v>
       </c>
       <c r="B5" t="n">
-        <v>58316</v>
+        <v>83290</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103001</v>
+        <v>6439</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1050,13 +1061,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>334513</v>
+        <v>334519</v>
       </c>
       <c r="R5" t="n">
-        <v>6432789</v>
+        <v>6432715</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1094,8 +1105,24 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1109,6 +1136,689 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130333857</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58388</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Frövehed, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>334513</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6432789</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131709468</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58250</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103019</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Stjärtmes</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Aegithalos caudatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Frövehed nordväst om, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>334577</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6432702</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Invid bäcken.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130333780</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Frövehed, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>334597</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6432745</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131709288</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58134</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Frövehed, nordväst om, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>334620</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6432747</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>I en al i sumpskogen ca 15 m öster om stengärdesgården.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131709342</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58134</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Frövehed nordväst om, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>334577</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6432702</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>I en klibbal nära bäcken.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130333842</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Frövehed, Vg</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>334546</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6432714</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60293-2025 artfynd.xlsx
+++ b/artfynd/A 60293-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130333753</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130333762</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130333833</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130333817</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1245,6 +1270,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130333857</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1359,6 +1389,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131709468</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1468,6 +1503,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130333780</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1592,6 +1632,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131709288</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1716,6 +1761,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131709342</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1819,8 +1869,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130333842</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>